--- a/generation_zy/sowo-物料1-1.xlsx
+++ b/generation_zy/sowo-物料1-1.xlsx
@@ -391,7 +391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="16.25" customWidth="1" min="1" max="1"/>
@@ -417,7 +417,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260924-001</t>
+          <t>20260922-001</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -430,13 +430,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260924-001</t>
+          <t>20261012-001</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20261012-001</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C4" t="n">
         <v>1</v>
       </c>
     </row>
